--- a/docs/entregables/ActReto02-propuesta-economica.xlsx
+++ b/docs/entregables/ActReto02-propuesta-economica.xlsx
@@ -65,7 +65,7 @@
     <t>CCTV-223</t>
   </si>
   <si>
-    <t>Camaras adicionales/rentadas para vigilancia del evento por SSID OMI-Camaras / VLAN 80. Costo de referencia Steren Mexico.</t>
+    <t>Camaras adicionales/rentadas para vigilancia del evento por SSID OMI-Camaras / VLAN 70. Costo de referencia Steren Mexico.</t>
   </si>
   <si>
     <t>SOPORTE-TI-2D</t>
